--- a/databaze_filmu.xlsx
+++ b/databaze_filmu.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c678b8341a1804/Dokumenty/carousely/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="240" documentId="13_ncr:1_{F0DD17AA-57C3-401E-A619-37D4E16B6A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A5C0E0F-EC59-45AA-96C0-5548B97AEAE3}"/>
+  <xr:revisionPtr revIDLastSave="294" documentId="13_ncr:1_{F0DD17AA-57C3-401E-A619-37D4E16B6A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{176CA5D8-DBC4-4344-9CCF-48964232C752}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="databaze_filmu" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">databaze_filmu!$A$1:$A$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">databaze_filmu!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3224" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3226" uniqueCount="186">
   <si>
     <t>Jen samé krásné věci</t>
   </si>
@@ -522,9 +522,6 @@
     <t>Blahoslavená rodina Ulmova</t>
   </si>
   <si>
-    <t>číslo</t>
-  </si>
-  <si>
     <t>Athos</t>
   </si>
   <si>
@@ -592,6 +589,15 @@
   </si>
   <si>
     <t>Nový duch</t>
+  </si>
+  <si>
+    <t>Zkušenost exorcisty</t>
+  </si>
+  <si>
+    <t>Odkrytý závoj</t>
+  </si>
+  <si>
+    <t>Priorita</t>
   </si>
 </sst>
 </file>
@@ -784,7 +790,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -834,17 +840,8 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1476,20 +1473,9 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="VŠECHNY_FILMY" displayName="VŠECHNY_FILMY" ref="A1:T170">
-  <autoFilter ref="A1:T170" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="TRUE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T170">
-    <sortCondition ref="A1:A170"/>
-  </sortState>
+  <autoFilter ref="A1:T170" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}"/>
   <tableColumns count="20">
-    <tableColumn id="5" xr3:uid="{B4048FE8-48A7-4A5F-8318-B61F55474511}" name="číslo" dataDxfId="16">
-      <calculatedColumnFormula>RAND()</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="17" xr3:uid="{9E94A714-F39E-4841-B60F-2788FA9E7806}" name="Priorita" dataDxfId="16"/>
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="film"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Obsah zdarma"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Náš výběr"/>
@@ -1719,7 +1705,7 @@
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="31.28515625" customWidth="1"/>
+    <col min="2" max="2" width="41.85546875" customWidth="1"/>
     <col min="4" max="4" width="29.42578125" customWidth="1"/>
     <col min="5" max="6" width="29.85546875" customWidth="1"/>
     <col min="7" max="7" width="21.28515625" customWidth="1"/>
@@ -1742,7 +1728,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>76</v>
@@ -1802,10 +1788,9 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="18">
-        <f t="shared" ref="A2:A33" ca="1" si="0">RAND()</f>
-        <v>0.56131895000087428</v>
+    <row r="2" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="9">
+        <v>2</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>57</v>
@@ -1865,10 +1850,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.11884082732671319</v>
+    <row r="3" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="6">
+        <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>29</v>
@@ -1925,13 +1909,12 @@
         <v>153</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.3201540440127042</v>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="6">
+        <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>6</v>
@@ -1940,7 +1923,7 @@
         <v>153</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>153</v>
@@ -1991,10 +1974,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.30019024750288592</v>
+    <row r="5" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="6">
+        <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>54</v>
@@ -2054,10 +2036,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.72668298833018763</v>
+    <row r="6" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="6">
+        <v>3</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>112</v>
@@ -2117,10 +2098,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.80307263875865631</v>
+    <row r="7" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="6">
+        <v>2</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>98</v>
@@ -2180,10 +2160,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.63531883990805471</v>
+    <row r="8" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
+        <v>5</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>104</v>
@@ -2243,10 +2222,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.40200148366477106</v>
+    <row r="9" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="6">
+        <v>2</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>48</v>
@@ -2306,10 +2284,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.40409063664739286</v>
+    <row r="10" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
+        <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>147</v>
@@ -2369,10 +2346,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.20313217245604376</v>
+    <row r="11" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
+        <v>1</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>150</v>
@@ -2432,10 +2408,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.11076356144614485</v>
+    <row r="12" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="6">
+        <v>1</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>145</v>
@@ -2495,10 +2470,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.57162049056511122</v>
+    <row r="13" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="6">
+        <v>3</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>123</v>
@@ -2558,13 +2532,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.31124754773189844</v>
+    <row r="14" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="6">
+        <v>3</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>153</v>
@@ -2622,9 +2595,8 @@
       </c>
     </row>
     <row r="15" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A15" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.29013224642469571</v>
+      <c r="A15" s="6">
+        <v>1</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>131</v>
@@ -2684,10 +2656,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.15513632680714473</v>
+    <row r="16" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A16" s="6">
+        <v>3</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>116</v>
@@ -2747,10 +2718,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.45792037956528142</v>
+    <row r="17" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A17" s="6">
+        <v>1</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>143</v>
@@ -2810,10 +2780,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.75022088293955147</v>
+    <row r="18" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A18" s="6">
+        <v>4</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>152</v>
@@ -2873,10 +2842,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.93766660618215969</v>
+    <row r="19" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A19" s="6">
+        <v>2</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>7</v>
@@ -2885,7 +2853,7 @@
         <v>153</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>153</v>
@@ -2936,10 +2904,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.69791234370536259</v>
+    <row r="20" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A20" s="6">
+        <v>3</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>115</v>
@@ -2999,10 +2966,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.4213226437789771</v>
+    <row r="21" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A21" s="6">
+        <v>1</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>141</v>
@@ -3062,10 +3028,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.44673155895267869</v>
+    <row r="22" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A22" s="6">
+        <v>1</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>62</v>
@@ -3125,10 +3090,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.61300993286841476</v>
+    <row r="23" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A23" s="6">
+        <v>1</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>87</v>
@@ -3188,10 +3152,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.74994037173939465</v>
+    <row r="24" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A24" s="6">
+        <v>1</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>89</v>
@@ -3200,7 +3163,7 @@
         <v>153</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>154</v>
@@ -3251,10 +3214,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.45244932307441965</v>
+    <row r="25" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="6">
+        <v>1</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>132</v>
@@ -3314,10 +3276,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.20586130570088412</v>
+    <row r="26" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A26" s="6">
+        <v>3</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
@@ -3326,7 +3287,7 @@
         <v>153</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>153</v>
@@ -3377,10 +3338,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.54203309719093506</v>
+    <row r="27" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A27" s="6">
+        <v>2</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>109</v>
@@ -3437,16 +3397,15 @@
         <v>153</v>
       </c>
       <c r="T27" s="6" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.54494816369420562</v>
-      </c>
-      <c r="B28" s="21" t="s">
-        <v>172</v>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A28" s="6">
+        <v>3</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>171</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>153</v>
@@ -3503,10 +3462,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.66336728066567052</v>
+    <row r="29" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A29" s="6">
+        <v>5</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>91</v>
@@ -3566,13 +3524,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.84948352571860852</v>
+    <row r="30" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A30" s="6">
+        <v>3</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>153</v>
@@ -3629,10 +3586,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>5.607640585618523E-2</v>
+    <row r="31" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A31" s="6">
+        <v>1</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>21</v>
@@ -3692,10 +3648,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.23645058889101456</v>
+    <row r="32" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A32" s="6">
+        <v>1</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>9</v>
@@ -3755,10 +3710,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="8">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.42810925047961856</v>
+    <row r="33" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A33" s="6">
+        <v>1</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>53</v>
@@ -3818,10 +3772,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="8">
-        <f t="shared" ref="A34:A65" ca="1" si="1">RAND()</f>
-        <v>0.6927176034640542</v>
+    <row r="34" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A34" s="6">
+        <v>3</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>122</v>
@@ -3881,10 +3834,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="35" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.81955851801447155</v>
+    <row r="35" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A35" s="6">
+        <v>2</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>45</v>
@@ -3944,10 +3896,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.66491315760834213</v>
+    <row r="36" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A36" s="6">
+        <v>1</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>130</v>
@@ -4004,13 +3955,12 @@
         <v>153</v>
       </c>
       <c r="T36" s="6" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.35576246987923843</v>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A37" s="6">
+        <v>5</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>110</v>
@@ -4070,10 +4020,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.20570458541962355</v>
+    <row r="38" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A38" s="6">
+        <v>5</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>127</v>
@@ -4133,10 +4082,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.72794033314332862</v>
+    <row r="39" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A39" s="6">
+        <v>3</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>31</v>
@@ -4196,10 +4144,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.22872710779440897</v>
+    <row r="40" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A40" s="6">
+        <v>2</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>159</v>
@@ -4260,9 +4207,8 @@
       </c>
     </row>
     <row r="41" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A41" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.76074872558348805</v>
+      <c r="A41" s="6">
+        <v>1</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>96</v>
@@ -4322,10 +4268,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.73801180099067276</v>
+    <row r="42" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A42" s="6">
+        <v>1</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>19</v>
@@ -4385,13 +4330,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.11001566746635871</v>
+    <row r="43" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A43" s="6">
+        <v>4</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>153</v>
@@ -4448,10 +4392,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.48247319260892163</v>
+    <row r="44" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A44" s="6">
+        <v>1</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>13</v>
@@ -4508,13 +4451,12 @@
         <v>153</v>
       </c>
       <c r="T44" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.65856550650463996</v>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A45" s="6">
+        <v>1</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>44</v>
@@ -4574,10 +4516,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.88869370633392863</v>
+    <row r="46" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A46" s="6">
+        <v>5</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>41</v>
@@ -4637,10 +4578,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.57460087699263418</v>
+    <row r="47" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A47" s="6">
+        <v>1</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>28</v>
@@ -4700,10 +4640,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="48" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.41289335517690184</v>
+    <row r="48" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A48" s="6">
+        <v>4</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>114</v>
@@ -4763,10 +4702,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.40041547831764268</v>
+    <row r="49" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A49" s="6">
+        <v>5</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>95</v>
@@ -4826,10 +4764,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.75487847181288914</v>
+    <row r="50" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A50" s="6">
+        <v>1</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>47</v>
@@ -4889,10 +4826,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.55947166534618165</v>
+    <row r="51" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A51" s="6">
+        <v>2</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>58</v>
@@ -4952,10 +4888,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="52" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.449603167417848</v>
+    <row r="52" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A52" s="6">
+        <v>3</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>40</v>
@@ -5015,10 +4950,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="53" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.35330499152905559</v>
+    <row r="53" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A53" s="6">
+        <v>2</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>99</v>
@@ -5078,16 +5012,15 @@
         <v>153</v>
       </c>
     </row>
-    <row r="54" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.93541450953564664</v>
+    <row r="54" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A54" s="6">
+        <v>1</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>111</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>153</v>
@@ -5141,10 +5074,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.71609359955229357</v>
+    <row r="55" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A55" s="6">
+        <v>1</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>135</v>
@@ -5204,10 +5136,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.84760480636344082</v>
+    <row r="56" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A56" s="6">
+        <v>1</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>25</v>
@@ -5267,19 +5198,18 @@
         <v>153</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.65367102306826597</v>
-      </c>
-      <c r="B57" s="21" t="s">
-        <v>171</v>
+    <row r="57" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="6">
+        <v>1</v>
+      </c>
+      <c r="B57" s="18" t="s">
+        <v>170</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>153</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>154</v>
@@ -5330,10 +5260,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="58" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.32290482548577415</v>
+    <row r="58" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A58" s="6">
+        <v>1</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>43</v>
@@ -5342,7 +5271,7 @@
         <v>153</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>154</v>
@@ -5393,10 +5322,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>1.3809031256545978E-2</v>
+    <row r="59" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="6">
+        <v>2</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>139</v>
@@ -5456,10 +5384,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="60" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.26560503669417868</v>
+    <row r="60" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="6">
+        <v>1</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>26</v>
@@ -5520,9 +5447,8 @@
       </c>
     </row>
     <row r="61" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A61" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.72146300890191017</v>
+      <c r="A61" s="6">
+        <v>1</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>37</v>
@@ -5583,15 +5509,14 @@
       </c>
     </row>
     <row r="62" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A62" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.947982759193435</v>
+      <c r="A62" s="6">
+        <v>2</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>121</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>153</v>
@@ -5645,10 +5570,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.82645520248558646</v>
+    <row r="63" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="6">
+        <v>2</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>137</v>
@@ -5708,10 +5632,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="64" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.99287772639623761</v>
+    <row r="64" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A64" s="6">
+        <v>5</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>126</v>
@@ -5771,10 +5694,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="65" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="8">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.76890431602130849</v>
+    <row r="65" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="6">
+        <v>1</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>30</v>
@@ -5834,10 +5756,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="66" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="8">
-        <f t="shared" ref="A66:A97" ca="1" si="2">RAND()</f>
-        <v>0.85094907142466469</v>
+    <row r="66" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A66" s="6">
+        <v>3</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>136</v>
@@ -5897,10 +5818,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="67" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.96900081382839998</v>
+    <row r="67" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A67" s="6">
+        <v>1</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>138</v>
@@ -5960,10 +5880,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="68" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.7995594114088016</v>
+    <row r="68" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A68" s="6">
+        <v>2</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>113</v>
@@ -6023,10 +5942,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="69" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.63837492907680526</v>
+    <row r="69" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A69" s="6">
+        <v>4</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>85</v>
@@ -6086,10 +6004,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="70" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.24551320082324934</v>
+    <row r="70" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A70" s="6">
+        <v>1</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>79</v>
@@ -6149,10 +6066,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="71" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>3.676946309415452E-2</v>
+    <row r="71" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A71" s="6">
+        <v>1</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>15</v>
@@ -6212,10 +6128,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="72" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.7189206715490678</v>
+    <row r="72" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A72" s="6">
+        <v>2</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>59</v>
@@ -6275,10 +6190,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="73" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.51202391628683208</v>
+    <row r="73" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A73" s="6">
+        <v>4</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>156</v>
@@ -6338,10 +6252,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="74" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.42142736139162851</v>
+    <row r="74" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A74" s="6">
+        <v>1</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>129</v>
@@ -6401,10 +6314,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="75" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.51410777687375753</v>
+    <row r="75" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A75" s="6">
+        <v>5</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>148</v>
@@ -6464,13 +6376,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="76" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.95396061405432953</v>
+    <row r="76" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A76" s="6">
+        <v>5</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>153</v>
@@ -6527,10 +6438,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="77" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.39420354444262495</v>
+    <row r="77" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A77" s="6">
+        <v>4</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>94</v>
@@ -6590,10 +6500,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="78" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.28693120359343305</v>
+    <row r="78" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A78" s="6">
+        <v>2</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>101</v>
@@ -6653,13 +6562,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="79" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.2285343209817069</v>
+    <row r="79" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A79" s="6">
+        <v>3</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>153</v>
@@ -6716,10 +6624,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="80" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.6857196534745128</v>
+    <row r="80" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A80" s="6">
+        <v>1</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>50</v>
@@ -6779,13 +6686,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="81" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.90510551160236818</v>
+    <row r="81" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A81" s="6">
+        <v>4</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>153</v>
@@ -6842,13 +6748,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>8.1074100168581742E-2</v>
+    <row r="82" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A82" s="6">
+        <v>3</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>153</v>
@@ -6905,13 +6810,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.78396219982386905</v>
+    <row r="83" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A83" s="6">
+        <v>1</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>153</v>
@@ -6968,10 +6872,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.89379098202099228</v>
+    <row r="84" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A84" s="6">
+        <v>3</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>119</v>
@@ -6980,7 +6883,7 @@
         <v>153</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>154</v>
@@ -7031,10 +6934,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>9.9540835564603136E-2</v>
+    <row r="85" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A85" s="6">
+        <v>4</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>23</v>
@@ -7094,10 +6996,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.61463577313106899</v>
+    <row r="86" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A86" s="6">
+        <v>3</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>117</v>
@@ -7157,10 +7058,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.14125290843094351</v>
+    <row r="87" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A87" s="6">
+        <v>2</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>17</v>
@@ -7221,12 +7121,11 @@
       </c>
     </row>
     <row r="88" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.7571194770741132</v>
+      <c r="A88" s="6">
+        <v>2</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>154</v>
@@ -7283,10 +7182,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="89" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>4.8092709127000366E-2</v>
+    <row r="89" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A89" s="6">
+        <v>4</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>134</v>
@@ -7346,13 +7244,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="90" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.53165020165687638</v>
-      </c>
-      <c r="B90" s="21" t="s">
-        <v>173</v>
+    <row r="90" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A90" s="6">
+        <v>1</v>
+      </c>
+      <c r="B90" s="18" t="s">
+        <v>172</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>153</v>
@@ -7409,10 +7306,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="91" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.89825869096537592</v>
+    <row r="91" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A91" s="6">
+        <v>1</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>118</v>
@@ -7421,7 +7317,7 @@
         <v>153</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E91" s="6" t="s">
         <v>153</v>
@@ -7469,13 +7365,12 @@
         <v>153</v>
       </c>
       <c r="T91" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="92" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.49931715874760618</v>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A92" s="6">
+        <v>2</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>103</v>
@@ -7535,10 +7430,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="93" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.63082951396802611</v>
+    <row r="93" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A93" s="6">
+        <v>1</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>34</v>
@@ -7598,10 +7492,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="94" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.34436631389024919</v>
+    <row r="94" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A94" s="6">
+        <v>2</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>125</v>
@@ -7661,10 +7554,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="95" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.85038672164470364</v>
+    <row r="95" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A95" s="6">
+        <v>2</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>102</v>
@@ -7724,10 +7616,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="96" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.37866004944059806</v>
+    <row r="96" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A96" s="6">
+        <v>2</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>149</v>
@@ -7787,10 +7678,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="97" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="8">
-        <f t="shared" ca="1" si="2"/>
-        <v>0.86403585354874257</v>
+    <row r="97" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A97" s="6">
+        <v>3</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>38</v>
@@ -7850,10 +7740,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="98" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="8">
-        <f t="shared" ref="A98:A129" ca="1" si="3">RAND()</f>
-        <v>0.43682808527160666</v>
+    <row r="98" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A98" s="6">
+        <v>1</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>55</v>
@@ -7913,10 +7802,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="99" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>4.5047510179202166E-2</v>
+    <row r="99" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A99" s="6">
+        <v>1</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>8</v>
@@ -7973,16 +7861,15 @@
         <v>153</v>
       </c>
       <c r="T99" s="6" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="100" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.81794159223574092</v>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="100" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A100" s="6">
+        <v>1</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>153</v>
@@ -8039,10 +7926,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.30495880055738178</v>
+    <row r="101" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A101" s="6">
+        <v>5</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>35</v>
@@ -8102,10 +7988,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.36721279031637299</v>
+    <row r="102" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A102" s="6">
+        <v>1</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>11</v>
@@ -8114,7 +7999,7 @@
         <v>153</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>153</v>
@@ -8165,10 +8050,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.43335581016939351</v>
+    <row r="103" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A103" s="6">
+        <v>2</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>22</v>
@@ -8228,10 +8112,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="104" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.50566143775732819</v>
+    <row r="104" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A104" s="6">
+        <v>2</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>84</v>
@@ -8291,10 +8174,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="105" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.99569191221347397</v>
+    <row r="105" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A105" s="6">
+        <v>1</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>77</v>
@@ -8354,10 +8236,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="106" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.59982864877726727</v>
+    <row r="106" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A106" s="6">
+        <v>3</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>158</v>
@@ -8417,10 +8298,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.90048783197926596</v>
+    <row r="107" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A107" s="6">
+        <v>4</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>83</v>
@@ -8480,10 +8360,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="108" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.2943438162225448</v>
+    <row r="108" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A108" s="6">
+        <v>1</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>51</v>
@@ -8543,10 +8422,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="109" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.75458037257893684</v>
+    <row r="109" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A109" s="6">
+        <v>5</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>36</v>
@@ -8606,13 +8484,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.33825562530743758</v>
+    <row r="110" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A110" s="6">
+        <v>1</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>153</v>
@@ -8669,10 +8546,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.93604525121117044</v>
+    <row r="111" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A111" s="6">
+        <v>1</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>49</v>
@@ -8732,10 +8608,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="112" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>3.375435807187166E-2</v>
+    <row r="112" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A112" s="6">
+        <v>3</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>120</v>
@@ -8795,10 +8670,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="113" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>6.781051746453659E-2</v>
+    <row r="113" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A113" s="6">
+        <v>1</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>140</v>
@@ -8858,10 +8732,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="114" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.10383243153597033</v>
+    <row r="114" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A114" s="6">
+        <v>1</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>142</v>
@@ -8921,10 +8794,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="115" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.50996415236341386</v>
+    <row r="115" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A115" s="6">
+        <v>4</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>86</v>
@@ -8984,10 +8856,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="116" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.16214916962433967</v>
+    <row r="116" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A116" s="6">
+        <v>5</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>81</v>
@@ -9047,10 +8918,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="117" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.73472477852915141</v>
+    <row r="117" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A117" s="6">
+        <v>3</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>157</v>
@@ -9110,10 +8980,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="118" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.74686532103330372</v>
+    <row r="118" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A118" s="6">
+        <v>1</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>80</v>
@@ -9122,7 +8991,7 @@
         <v>153</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>154</v>
@@ -9174,9 +9043,8 @@
       </c>
     </row>
     <row r="119" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A119" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.54966684377843711</v>
+      <c r="A119" s="6">
+        <v>2</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>106</v>
@@ -9236,10 +9104,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="120" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.95205634622667423</v>
+    <row r="120" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A120" s="6">
+        <v>1</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>32</v>
@@ -9299,10 +9166,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="121" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.66590812941555222</v>
+    <row r="121" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A121" s="6">
+        <v>1</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>1</v>
@@ -9362,10 +9228,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="122" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.45391295552704725</v>
+    <row r="122" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A122" s="6">
+        <v>4</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>92</v>
@@ -9425,10 +9290,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="123" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.84777467771142134</v>
+    <row r="123" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A123" s="6">
+        <v>3</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>24</v>
@@ -9488,10 +9352,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="124" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.89734780723948027</v>
+    <row r="124" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A124" s="6">
+        <v>1</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>78</v>
@@ -9552,9 +9415,8 @@
       </c>
     </row>
     <row r="125" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A125" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.58717063355476562</v>
+      <c r="A125" s="6">
+        <v>1</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>133</v>
@@ -9615,9 +9477,8 @@
       </c>
     </row>
     <row r="126" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A126" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.15258015437269346</v>
+      <c r="A126" s="6">
+        <v>1</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>151</v>
@@ -9677,10 +9538,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="127" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.57452449916336445</v>
+    <row r="127" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A127" s="6">
+        <v>2</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>100</v>
@@ -9740,10 +9600,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="128" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.5705723661316594</v>
+    <row r="128" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A128" s="6">
+        <v>1</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>46</v>
@@ -9803,13 +9662,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="129" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="8">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.5398667394047485</v>
+    <row r="129" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A129" s="6">
+        <v>1</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>153</v>
@@ -9866,10 +9724,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="130" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="8">
-        <f t="shared" ref="A130:A163" ca="1" si="4">RAND()</f>
-        <v>0.57420455349983723</v>
+    <row r="130" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A130" s="6">
+        <v>4</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>88</v>
@@ -9929,10 +9786,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="131" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.56313722145167244</v>
+    <row r="131" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A131" s="6">
+        <v>2</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>90</v>
@@ -9992,10 +9848,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="132" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>6.1316204577569922E-2</v>
+    <row r="132" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A132" s="6">
+        <v>1</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>155</v>
@@ -10055,10 +9910,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="133" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.83457736297307317</v>
+    <row r="133" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A133" s="6">
+        <v>3</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>39</v>
@@ -10118,10 +9972,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="134" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.15273790877237492</v>
+    <row r="134" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A134" s="6">
+        <v>1</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>16</v>
@@ -10181,10 +10034,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="135" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.44130997173697684</v>
+    <row r="135" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A135" s="6">
+        <v>1</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>61</v>
@@ -10244,10 +10096,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="136" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.26383700577628622</v>
+    <row r="136" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A136" s="6">
+        <v>1</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>108</v>
@@ -10307,10 +10158,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="137" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.52663047455742384</v>
+    <row r="137" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A137" s="6">
+        <v>1</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>60</v>
@@ -10370,10 +10220,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="138" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.75477865303817793</v>
+    <row r="138" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A138" s="6">
+        <v>4</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>124</v>
@@ -10433,13 +10282,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="139" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.97204838307179686</v>
+    <row r="139" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A139" s="6">
+        <v>2</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>153</v>
@@ -10496,10 +10344,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="140" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>6.791335308520341E-2</v>
+    <row r="140" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A140" s="6">
+        <v>5</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>105</v>
@@ -10559,10 +10406,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="141" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.7342040612202172</v>
+    <row r="141" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A141" s="6">
+        <v>5</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>128</v>
@@ -10623,12 +10469,11 @@
       </c>
     </row>
     <row r="142" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A142" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>7.7307422430512696E-2</v>
+      <c r="A142" s="6">
+        <v>1</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>154</v>
@@ -10685,10 +10530,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="143" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.61117532867474367</v>
+    <row r="143" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A143" s="6">
+        <v>1</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>56</v>
@@ -10748,10 +10592,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="144" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.8614083110047891</v>
+    <row r="144" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A144" s="6">
+        <v>4</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>144</v>
@@ -10811,13 +10654,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="145" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>6.6279104673826472E-2</v>
+    <row r="145" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A145" s="6">
+        <v>3</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>153</v>
@@ -10874,10 +10716,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="146" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.12930571351915998</v>
+    <row r="146" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A146" s="6">
+        <v>1</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>93</v>
@@ -10937,10 +10778,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="147" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.35249475747024628</v>
+    <row r="147" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A147" s="6">
+        <v>2</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>4</v>
@@ -11000,10 +10840,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="148" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.94528202823968588</v>
+    <row r="148" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A148" s="6">
+        <v>1</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>52</v>
@@ -11063,10 +10902,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="149" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A149" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>3.6615099738946943E-3</v>
+    <row r="149" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A149" s="6">
+        <v>1</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>18</v>
@@ -11126,10 +10964,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="150" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A150" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>7.7071523648872708E-2</v>
+    <row r="150" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A150" s="6">
+        <v>1</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>33</v>
@@ -11189,10 +11026,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="151" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.13037286265455705</v>
+    <row r="151" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A151" s="6">
+        <v>1</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>0</v>
@@ -11252,10 +11088,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="152" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.5139694349959314</v>
+    <row r="152" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A152" s="6">
+        <v>1</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>97</v>
@@ -11315,10 +11150,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="153" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.94173661870212222</v>
+    <row r="153" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A153" s="6">
+        <v>1</v>
       </c>
       <c r="B153" s="5" t="s">
         <v>42</v>
@@ -11378,10 +11212,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="154" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.24614662446346702</v>
+    <row r="154" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A154" s="6">
+        <v>1</v>
       </c>
       <c r="B154" s="5" t="s">
         <v>146</v>
@@ -11441,10 +11274,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="155" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.70925963361743982</v>
+    <row r="155" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A155" s="6">
+        <v>1</v>
       </c>
       <c r="B155" s="5" t="s">
         <v>27</v>
@@ -11504,10 +11336,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="156" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.34812794088505594</v>
+    <row r="156" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A156" s="6">
+        <v>2</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>107</v>
@@ -11567,10 +11398,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="157" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.87119821456243796</v>
+    <row r="157" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A157" s="6">
+        <v>1</v>
       </c>
       <c r="B157" s="5" t="s">
         <v>82</v>
@@ -11630,10 +11460,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="158" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.37737696975596779</v>
+    <row r="158" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A158" s="6">
+        <v>1</v>
       </c>
       <c r="B158" s="5" t="s">
         <v>20</v>
@@ -11693,324 +11522,323 @@
         <v>153</v>
       </c>
     </row>
-    <row r="159" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.73273687697316003</v>
+    <row r="159" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A159" s="6">
+        <v>2</v>
       </c>
       <c r="B159" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D159" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E159" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="F159" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G159" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H159" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="I159" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="J159" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="K159" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="L159" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="M159" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="N159" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="O159" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="P159" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q159" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="R159" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="S159" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="T159" s="6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="160" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A160" s="6">
+        <v>2</v>
+      </c>
+      <c r="B160" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="C159" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D159" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E159" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="F159" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="G159" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="H159" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="I159" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="J159" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="K159" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="L159" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="M159" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="N159" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="O159" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="P159" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q159" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="R159" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="S159" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="T159" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="160" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.59442329020288742</v>
-      </c>
-      <c r="B160" s="5" t="s">
+      <c r="C160" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E160" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F160" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="G160" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H160" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="I160" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="J160" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="K160" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="L160" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="M160" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="N160" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="O160" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="P160" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q160" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="R160" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="S160" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="T160" s="6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="161" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A161" s="6">
+        <v>3</v>
+      </c>
+      <c r="B161" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="C160" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D160" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E160" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F160" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="G160" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="H160" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="I160" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="J160" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="K160" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="L160" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="M160" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="N160" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="O160" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="P160" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q160" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="R160" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="S160" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="T160" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="161" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.38822066761868679</v>
-      </c>
-      <c r="B161" s="5" t="s">
+      <c r="C161" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E161" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F161" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="G161" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H161" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="I161" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="J161" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="K161" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="L161" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="M161" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="N161" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="O161" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="P161" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q161" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="R161" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="S161" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="T161" s="6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="162" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A162" s="6">
+        <v>1</v>
+      </c>
+      <c r="B162" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="C161" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D161" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E161" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F161" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="G161" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="H161" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="I161" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="J161" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="K161" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="L161" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="M161" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="N161" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="O161" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="P161" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q161" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="R161" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="S161" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="T161" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="162" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.54630801284317398</v>
-      </c>
-      <c r="B162" s="5" t="s">
+      <c r="C162" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E162" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="F162" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G162" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H162" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="I162" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="J162" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="K162" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="L162" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="M162" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="N162" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="O162" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="P162" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q162" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="R162" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="S162" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="T162" s="6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="163" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A163" s="6">
+        <v>1</v>
+      </c>
+      <c r="B163" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C162" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D162" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E162" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="F162" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="G162" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="H162" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="I162" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="J162" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="K162" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="L162" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="M162" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="N162" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="O162" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="P162" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q162" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="R162" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="S162" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="T162" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="163" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="8">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.61656980355869995</v>
-      </c>
-      <c r="B163" s="5" t="s">
+      <c r="C163" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E163" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="F163" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G163" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H163" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="I163" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="J163" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="K163" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="L163" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="M163" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="N163" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="O163" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="P163" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q163" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="R163" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="S163" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="T163" s="6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="164" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A164" s="6">
+        <v>2</v>
+      </c>
+      <c r="B164" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="C163" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D163" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E163" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="F163" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="G163" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="H163" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="I163" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="J163" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="K163" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="L163" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="M163" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="N163" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="O163" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="P163" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q163" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="R163" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="S163" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="T163" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="164" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="8"/>
-      <c r="B164" s="5"/>
       <c r="C164" s="6" t="s">
         <v>153</v>
       </c>
@@ -12039,7 +11867,7 @@
         <v>153</v>
       </c>
       <c r="L164" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M164" s="5" t="s">
         <v>153</v>
@@ -12051,7 +11879,7 @@
         <v>153</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q164" s="6" t="s">
         <v>153</v>
@@ -12060,23 +11888,27 @@
         <v>153</v>
       </c>
       <c r="S164" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="T164" s="6" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="165" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A165" s="8"/>
-      <c r="B165" s="5"/>
+    <row r="165" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A165" s="6">
+        <v>1</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="C165" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D165" s="6" t="s">
         <v>153</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F165" s="6" t="s">
         <v>153</v>
@@ -12118,14 +11950,14 @@
         <v>153</v>
       </c>
       <c r="S165" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="T165" s="6" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="166" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="8"/>
+    <row r="166" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A166" s="6"/>
       <c r="B166" s="5"/>
       <c r="C166" s="6" t="s">
         <v>153</v>
@@ -12182,8 +12014,8 @@
         <v>153</v>
       </c>
     </row>
-    <row r="167" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A167" s="8"/>
+    <row r="167" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A167" s="6"/>
       <c r="B167" s="5"/>
       <c r="C167" s="6" t="s">
         <v>153</v>
@@ -12240,8 +12072,8 @@
         <v>153</v>
       </c>
     </row>
-    <row r="168" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A168" s="8"/>
+    <row r="168" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A168" s="6"/>
       <c r="B168" s="5"/>
       <c r="C168" s="6" t="s">
         <v>153</v>
@@ -12298,8 +12130,8 @@
         <v>153</v>
       </c>
     </row>
-    <row r="169" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="17"/>
+    <row r="169" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A169" s="6"/>
       <c r="B169" s="5"/>
       <c r="C169" s="6" t="s">
         <v>153</v>
@@ -12356,9 +12188,9 @@
         <v>153</v>
       </c>
     </row>
-    <row r="170" spans="1:20" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A170" s="20"/>
-      <c r="B170" s="19"/>
+    <row r="170" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A170" s="10"/>
+      <c r="B170" s="17"/>
       <c r="C170" s="6" t="s">
         <v>153</v>
       </c>
@@ -12442,9 +12274,6 @@
     <row r="196" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="197" ht="12.75" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A170">
-    <sortCondition ref="A2:A170"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <tableParts count="1">

--- a/databaze_filmu.xlsx
+++ b/databaze_filmu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c678b8341a1804/Dokumenty/carousely/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="294" documentId="13_ncr:1_{F0DD17AA-57C3-401E-A619-37D4E16B6A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{176CA5D8-DBC4-4344-9CCF-48964232C752}"/>
+  <xr:revisionPtr revIDLastSave="312" documentId="13_ncr:1_{F0DD17AA-57C3-401E-A619-37D4E16B6A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1B80C03-F1EE-4AAC-9BCF-4AB0224D9A02}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3226" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3229" uniqueCount="189">
   <si>
     <t>Jen samé krásné věci</t>
   </si>
@@ -598,6 +598,15 @@
   </si>
   <si>
     <t>Priorita</t>
+  </si>
+  <si>
+    <t>Na jedné cestě</t>
+  </si>
+  <si>
+    <t>Polykarp: Ničitel božstev</t>
+  </si>
+  <si>
+    <t>Svědectví života</t>
   </si>
 </sst>
 </file>
@@ -11592,7 +11601,7 @@
         <v>179</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D160" s="6" t="s">
         <v>153</v>
@@ -11957,8 +11966,12 @@
       </c>
     </row>
     <row r="166" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A166" s="6"/>
-      <c r="B166" s="5"/>
+      <c r="A166" s="6">
+        <v>4</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>186</v>
+      </c>
       <c r="C166" s="6" t="s">
         <v>153</v>
       </c>
@@ -11999,7 +12012,7 @@
         <v>153</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q166" s="6" t="s">
         <v>153</v>
@@ -12008,15 +12021,19 @@
         <v>153</v>
       </c>
       <c r="S166" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="T166" s="6" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="167" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A167" s="6"/>
-      <c r="B167" s="5"/>
+      <c r="A167" s="6">
+        <v>1</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>187</v>
+      </c>
       <c r="C167" s="6" t="s">
         <v>153</v>
       </c>
@@ -12024,7 +12041,7 @@
         <v>153</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F167" s="6" t="s">
         <v>153</v>
@@ -12039,7 +12056,7 @@
         <v>153</v>
       </c>
       <c r="J167" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K167" s="6" t="s">
         <v>153</v>
@@ -12073,8 +12090,12 @@
       </c>
     </row>
     <row r="168" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A168" s="6"/>
-      <c r="B168" s="5"/>
+      <c r="A168" s="6">
+        <v>1</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>188</v>
+      </c>
       <c r="C168" s="6" t="s">
         <v>153</v>
       </c>
@@ -12118,7 +12139,7 @@
         <v>153</v>
       </c>
       <c r="Q168" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="R168" s="6" t="s">
         <v>153</v>

--- a/databaze_filmu.xlsx
+++ b/databaze_filmu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c678b8341a1804/Dokumenty/film-layout-manager_v2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="669" documentId="13_ncr:1_{F0DD17AA-57C3-401E-A619-37D4E16B6A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23393795-083C-4A17-9BC3-6FC5FE582C52}"/>
+  <xr:revisionPtr revIDLastSave="693" documentId="13_ncr:1_{F0DD17AA-57C3-401E-A619-37D4E16B6A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB9B547E-BC12-4158-9B99-FF46675120AA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="databaze_filmu" sheetId="3" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2826" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3883" uniqueCount="179">
   <si>
     <t>Jen samé krásné věci</t>
   </si>
@@ -568,6 +568,15 @@
   </si>
   <si>
     <t>Openheart podcast</t>
+  </si>
+  <si>
+    <t>Garabandal</t>
+  </si>
+  <si>
+    <t>Úžasná láska</t>
+  </si>
+  <si>
+    <t>Bula a Drbola</t>
   </si>
 </sst>
 </file>
@@ -1435,8 +1444,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="VŠECHNY_FILMY" displayName="VŠECHNY_FILMY" ref="A1:S157">
-  <autoFilter ref="A1:S157" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="VŠECHNY_FILMY" displayName="VŠECHNY_FILMY" ref="A1:S219">
+  <autoFilter ref="A1:S219" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}"/>
   <tableColumns count="19">
     <tableColumn id="17" xr3:uid="{9E94A714-F39E-4841-B60F-2788FA9E7806}" name="Priorita" dataDxfId="16"/>
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="film"/>
@@ -1663,7 +1672,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:S157"/>
+  <dimension ref="A1:S219"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -10900,21 +10909,26 @@
       </c>
     </row>
     <row r="157" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="8"/>
+      <c r="A157" s="8">
+        <v>1</v>
+      </c>
+      <c r="B157" t="s">
+        <v>176</v>
+      </c>
       <c r="C157" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D157" s="8" t="s">
         <v>114</v>
       </c>
       <c r="E157" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F157" s="8" t="s">
         <v>114</v>
       </c>
       <c r="G157" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H157" s="8" t="s">
         <v>114</v>
@@ -10950,6 +10964,3364 @@
         <v>114</v>
       </c>
       <c r="S157" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="158" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A158" s="8">
+        <v>1</v>
+      </c>
+      <c r="B158" t="s">
+        <v>177</v>
+      </c>
+      <c r="C158" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D158" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="E158" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F158" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H158" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="I158" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J158" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K158" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="L158" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M158" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N158" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O158" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P158" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q158" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R158" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S158" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="159" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="8">
+        <v>1</v>
+      </c>
+      <c r="B159" t="s">
+        <v>178</v>
+      </c>
+      <c r="C159" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D159" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E159" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F159" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="G159" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H159" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I159" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="J159" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="K159" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="L159" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="M159" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N159" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O159" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P159" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q159" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="R159" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S159" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="160" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="8"/>
+      <c r="C160" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D160" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E160" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F160" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G160" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H160" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I160" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J160" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K160" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L160" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M160" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N160" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O160" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P160" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q160" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R160" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S160" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="161" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A161" s="8"/>
+      <c r="C161" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D161" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E161" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F161" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G161" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H161" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I161" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J161" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K161" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L161" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M161" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N161" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O161" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P161" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q161" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R161" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S161" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="162" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A162" s="8"/>
+      <c r="C162" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D162" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E162" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F162" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G162" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H162" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I162" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J162" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K162" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L162" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M162" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N162" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O162" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P162" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q162" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R162" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S162" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="163" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A163" s="8"/>
+      <c r="C163" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D163" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E163" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F163" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G163" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H163" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I163" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J163" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K163" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L163" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M163" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N163" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O163" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P163" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q163" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R163" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S163" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="164" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A164" s="8"/>
+      <c r="C164" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D164" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E164" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F164" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G164" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H164" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I164" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J164" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K164" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L164" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M164" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N164" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O164" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P164" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q164" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R164" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S164" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="165" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A165" s="8"/>
+      <c r="C165" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D165" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E165" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F165" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G165" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H165" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I165" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J165" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K165" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L165" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M165" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N165" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O165" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P165" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q165" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R165" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S165" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="166" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A166" s="8"/>
+      <c r="C166" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D166" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E166" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F166" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G166" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H166" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I166" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J166" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K166" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L166" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M166" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N166" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O166" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P166" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q166" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R166" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S166" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="167" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A167" s="8"/>
+      <c r="C167" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D167" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E167" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F167" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G167" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H167" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I167" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J167" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K167" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L167" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M167" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N167" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O167" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P167" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q167" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R167" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S167" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="168" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A168" s="8"/>
+      <c r="C168" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D168" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E168" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F168" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G168" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H168" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I168" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J168" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K168" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L168" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M168" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N168" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O168" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P168" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q168" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R168" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S168" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="169" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A169" s="8"/>
+      <c r="C169" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D169" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E169" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F169" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G169" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H169" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I169" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J169" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K169" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L169" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M169" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N169" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O169" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P169" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q169" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R169" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S169" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="170" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A170" s="8"/>
+      <c r="C170" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D170" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E170" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F170" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G170" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H170" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I170" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J170" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K170" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L170" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M170" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N170" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O170" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P170" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q170" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R170" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S170" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="171" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A171" s="8"/>
+      <c r="C171" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D171" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E171" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F171" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G171" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H171" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I171" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J171" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K171" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L171" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M171" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N171" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O171" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P171" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q171" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R171" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S171" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="172" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A172" s="8"/>
+      <c r="C172" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D172" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E172" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F172" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G172" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H172" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I172" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J172" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K172" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L172" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M172" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N172" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O172" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P172" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q172" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R172" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S172" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="173" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A173" s="8"/>
+      <c r="C173" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D173" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E173" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F173" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G173" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H173" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I173" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J173" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K173" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L173" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M173" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N173" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O173" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P173" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q173" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R173" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S173" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="174" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A174" s="8"/>
+      <c r="C174" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D174" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E174" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F174" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G174" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H174" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I174" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J174" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K174" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L174" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M174" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N174" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O174" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P174" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q174" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R174" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S174" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="175" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A175" s="8"/>
+      <c r="C175" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D175" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E175" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F175" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G175" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H175" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I175" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J175" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K175" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L175" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M175" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N175" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O175" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P175" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q175" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R175" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S175" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="176" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A176" s="8"/>
+      <c r="C176" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D176" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E176" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F176" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G176" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H176" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I176" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J176" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K176" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L176" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M176" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N176" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O176" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P176" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q176" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R176" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S176" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="177" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A177" s="8"/>
+      <c r="C177" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D177" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E177" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F177" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G177" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H177" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I177" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J177" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K177" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L177" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M177" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N177" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O177" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P177" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q177" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R177" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S177" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="178" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A178" s="8"/>
+      <c r="C178" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D178" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E178" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F178" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G178" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H178" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I178" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J178" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K178" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L178" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M178" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N178" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O178" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P178" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q178" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R178" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S178" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="179" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A179" s="8"/>
+      <c r="C179" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D179" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E179" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F179" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G179" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H179" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I179" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J179" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K179" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L179" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M179" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N179" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O179" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P179" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q179" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R179" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S179" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="180" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A180" s="8"/>
+      <c r="C180" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D180" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E180" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F180" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G180" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H180" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I180" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J180" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K180" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L180" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M180" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N180" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O180" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P180" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q180" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R180" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S180" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="181" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A181" s="8"/>
+      <c r="C181" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D181" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E181" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F181" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G181" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H181" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I181" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J181" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K181" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L181" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M181" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N181" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O181" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P181" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q181" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R181" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S181" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="182" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A182" s="8"/>
+      <c r="C182" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D182" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E182" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F182" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G182" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H182" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I182" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J182" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K182" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L182" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M182" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N182" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O182" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P182" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q182" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R182" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S182" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="183" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A183" s="8"/>
+      <c r="C183" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D183" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E183" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F183" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G183" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H183" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I183" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J183" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K183" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L183" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M183" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N183" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O183" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P183" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q183" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R183" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S183" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="184" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A184" s="8"/>
+      <c r="C184" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D184" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E184" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F184" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G184" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H184" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I184" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J184" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K184" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L184" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M184" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N184" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O184" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P184" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q184" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R184" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S184" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="185" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A185" s="8"/>
+      <c r="C185" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D185" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E185" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F185" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G185" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H185" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I185" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J185" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K185" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L185" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M185" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N185" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O185" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P185" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q185" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R185" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S185" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="186" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A186" s="8"/>
+      <c r="C186" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D186" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E186" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F186" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G186" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H186" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I186" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J186" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K186" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L186" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M186" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N186" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O186" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P186" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q186" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R186" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S186" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="187" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A187" s="8"/>
+      <c r="C187" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D187" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E187" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F187" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G187" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H187" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I187" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J187" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K187" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L187" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M187" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N187" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O187" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P187" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q187" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R187" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S187" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="188" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A188" s="8"/>
+      <c r="C188" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D188" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E188" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F188" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G188" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H188" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I188" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J188" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K188" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L188" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M188" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N188" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O188" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P188" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q188" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R188" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S188" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="189" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A189" s="8"/>
+      <c r="C189" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D189" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E189" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F189" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G189" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H189" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I189" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J189" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K189" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L189" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M189" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N189" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O189" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P189" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q189" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R189" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S189" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="190" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A190" s="8"/>
+      <c r="C190" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D190" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E190" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F190" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G190" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H190" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I190" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J190" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K190" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L190" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M190" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N190" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O190" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P190" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q190" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R190" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S190" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="191" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A191" s="8"/>
+      <c r="C191" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D191" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E191" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F191" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G191" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H191" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I191" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J191" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K191" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L191" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M191" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N191" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O191" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P191" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q191" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R191" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S191" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="192" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A192" s="8"/>
+      <c r="C192" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D192" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E192" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F192" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G192" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H192" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I192" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J192" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K192" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L192" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M192" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N192" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O192" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P192" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q192" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R192" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S192" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="193" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A193" s="8"/>
+      <c r="C193" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D193" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E193" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F193" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G193" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H193" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I193" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J193" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K193" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L193" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M193" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N193" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O193" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P193" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q193" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R193" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S193" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="194" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A194" s="8"/>
+      <c r="C194" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D194" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E194" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F194" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G194" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H194" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I194" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J194" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K194" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L194" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M194" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N194" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O194" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P194" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q194" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R194" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S194" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="195" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A195" s="8"/>
+      <c r="C195" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D195" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E195" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F195" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G195" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H195" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I195" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J195" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K195" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L195" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M195" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N195" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O195" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P195" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q195" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R195" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S195" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="196" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A196" s="8"/>
+      <c r="C196" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D196" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E196" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F196" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G196" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H196" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I196" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J196" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K196" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L196" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M196" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N196" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O196" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P196" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q196" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R196" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S196" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="197" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A197" s="8"/>
+      <c r="C197" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D197" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E197" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F197" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G197" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H197" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I197" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J197" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K197" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L197" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M197" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N197" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O197" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P197" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q197" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R197" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S197" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="198" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A198" s="8"/>
+      <c r="C198" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D198" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E198" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F198" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G198" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H198" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I198" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J198" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K198" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L198" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M198" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N198" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O198" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P198" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q198" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R198" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S198" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="199" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A199" s="8"/>
+      <c r="C199" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D199" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E199" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F199" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G199" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H199" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I199" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J199" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K199" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L199" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M199" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N199" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O199" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P199" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q199" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R199" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S199" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="200" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A200" s="8"/>
+      <c r="C200" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D200" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E200" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F200" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G200" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H200" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I200" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J200" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K200" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L200" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M200" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N200" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O200" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P200" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q200" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R200" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S200" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="201" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A201" s="8"/>
+      <c r="C201" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D201" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E201" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F201" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G201" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H201" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I201" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J201" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K201" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L201" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M201" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N201" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O201" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P201" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q201" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R201" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S201" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="202" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A202" s="8"/>
+      <c r="C202" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D202" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E202" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F202" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G202" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H202" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I202" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J202" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K202" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L202" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M202" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N202" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O202" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P202" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q202" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R202" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S202" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="203" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A203" s="8"/>
+      <c r="C203" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D203" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E203" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F203" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G203" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H203" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I203" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J203" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K203" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L203" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M203" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N203" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O203" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P203" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q203" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R203" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S203" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="204" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A204" s="8"/>
+      <c r="C204" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D204" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E204" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F204" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G204" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H204" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I204" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J204" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K204" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L204" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M204" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N204" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O204" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P204" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q204" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R204" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S204" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="205" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A205" s="8"/>
+      <c r="C205" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D205" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E205" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F205" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G205" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H205" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I205" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J205" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K205" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L205" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M205" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N205" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O205" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P205" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q205" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R205" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S205" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="206" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A206" s="8"/>
+      <c r="C206" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D206" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E206" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F206" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G206" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H206" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I206" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J206" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K206" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L206" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M206" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N206" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O206" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P206" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q206" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R206" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S206" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="207" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A207" s="8"/>
+      <c r="C207" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D207" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E207" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F207" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G207" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H207" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I207" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J207" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K207" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L207" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M207" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N207" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O207" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P207" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q207" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R207" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S207" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="208" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A208" s="8"/>
+      <c r="C208" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D208" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E208" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F208" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G208" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H208" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I208" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J208" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K208" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L208" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M208" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N208" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O208" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P208" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q208" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R208" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S208" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="209" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A209" s="8"/>
+      <c r="C209" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D209" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E209" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F209" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G209" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H209" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I209" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J209" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K209" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L209" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M209" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N209" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O209" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P209" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q209" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R209" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S209" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="210" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A210" s="8"/>
+      <c r="C210" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D210" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E210" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F210" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G210" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H210" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I210" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J210" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K210" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L210" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M210" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N210" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O210" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P210" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q210" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R210" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S210" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="211" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A211" s="8"/>
+      <c r="C211" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D211" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E211" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F211" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G211" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H211" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I211" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J211" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K211" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L211" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M211" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N211" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O211" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P211" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q211" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R211" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S211" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="212" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A212" s="8"/>
+      <c r="C212" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D212" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E212" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F212" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G212" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H212" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I212" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J212" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K212" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L212" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M212" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N212" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O212" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P212" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q212" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R212" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S212" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="213" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A213" s="8"/>
+      <c r="C213" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D213" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E213" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F213" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G213" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H213" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I213" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J213" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K213" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L213" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M213" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N213" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O213" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P213" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q213" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R213" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S213" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="214" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A214" s="8"/>
+      <c r="C214" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D214" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E214" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F214" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G214" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H214" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I214" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J214" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K214" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L214" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M214" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N214" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O214" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P214" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q214" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R214" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S214" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="215" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A215" s="8"/>
+      <c r="C215" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D215" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E215" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F215" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G215" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H215" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I215" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J215" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K215" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L215" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M215" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N215" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O215" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P215" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q215" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R215" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S215" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="216" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A216" s="8"/>
+      <c r="C216" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D216" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E216" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F216" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G216" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H216" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I216" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J216" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K216" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L216" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M216" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N216" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O216" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P216" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q216" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R216" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S216" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="217" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A217" s="8"/>
+      <c r="C217" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D217" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E217" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F217" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G217" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H217" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I217" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J217" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K217" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L217" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M217" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N217" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O217" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P217" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q217" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R217" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S217" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="218" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A218" s="8"/>
+      <c r="C218" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D218" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E218" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F218" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G218" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H218" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I218" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J218" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K218" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L218" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M218" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N218" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O218" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P218" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q218" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R218" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S218" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="219" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A219" s="8"/>
+      <c r="C219" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D219" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E219" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F219" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G219" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H219" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I219" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J219" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K219" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L219" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M219" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="N219" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O219" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P219" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q219" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R219" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S219" s="17" t="s">
         <v>114</v>
       </c>
     </row>

--- a/databaze_filmu.xlsx
+++ b/databaze_filmu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c678b8341a1804/Dokumenty/film-layout-manager_v3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="971" documentId="13_ncr:1_{F0DD17AA-57C3-401E-A619-37D4E16B6A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4261557F-97F5-4005-A70D-71B959D714D7}"/>
+  <xr:revisionPtr revIDLastSave="987" documentId="13_ncr:1_{F0DD17AA-57C3-401E-A619-37D4E16B6A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB3EB910-57F0-4C6D-BE2F-CDDE2A71A3E9}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="databaze_filmu" sheetId="3" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4217" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4219" uniqueCount="181">
   <si>
     <t>Jen samé krásné věci</t>
   </si>
@@ -577,6 +577,12 @@
   </si>
   <si>
     <t>ID</t>
+  </si>
+  <si>
+    <t>Bod zlomu</t>
+  </si>
+  <si>
+    <t>Babettina hostina</t>
   </si>
 </sst>
 </file>
@@ -837,62 +843,6 @@
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="28">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1528,6 +1478,62 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF8F9FA"/>
@@ -1603,29 +1609,29 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="VŠECHNY_FILMY" displayName="VŠECHNY_FILMY" ref="A1:W203">
   <autoFilter ref="A1:W203" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}"/>
   <tableColumns count="23">
-    <tableColumn id="21" xr3:uid="{AFA04DCF-6DDB-4478-A6A0-E666816366F4}" name="ID" dataDxfId="1"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Film" dataDxfId="0"/>
-    <tableColumn id="17" xr3:uid="{9E94A714-F39E-4841-B60F-2788FA9E7806}" name="Priorita" dataDxfId="21"/>
+    <tableColumn id="21" xr3:uid="{AFA04DCF-6DDB-4478-A6A0-E666816366F4}" name="ID" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Film" dataDxfId="20"/>
+    <tableColumn id="17" xr3:uid="{9E94A714-F39E-4841-B60F-2788FA9E7806}" name="Priorita" dataDxfId="19"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Obsah zdarma"/>
-    <tableColumn id="19" xr3:uid="{C1D13260-4B9E-44ED-9D0B-CF10168DB7C7}" name="Plná velikost 1" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Náš výběr" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Křesťanské filmy" dataDxfId="18"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Filmy na základě skutečnosti" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Originální produkce" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Drama" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Biblické filmy" dataDxfId="14"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0100-000016000000}" name="Pro děti" dataDxfId="13"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Životopisné filmy" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Rodinné filmy" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="České a slovenské filmy" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{9FCF2ECA-C3A0-43A8-A186-FD04B39FEE7B}" name="Plná velikost 2" dataDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Filmy s dabingem" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Dokumenty" dataDxfId="7"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Seriály" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Krátké filmy" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{BCC4A0AC-A4A9-436F-978E-493A75355B9F}" name="Poutnické filmy" dataDxfId="4"/>
-    <tableColumn id="23" xr3:uid="{02EEE25E-FE38-4681-9DDC-8551467119E3}" name="Misijní filmy" dataDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{0DCBE57E-EFCC-47FB-ACE3-E37987A22685}" name="Plná velikost 3" dataDxfId="2"/>
+    <tableColumn id="19" xr3:uid="{C1D13260-4B9E-44ED-9D0B-CF10168DB7C7}" name="Plná velikost 1" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Náš výběr" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Křesťanské filmy" dataDxfId="16"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="Filmy na základě skutečnosti" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Originální produkce" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Drama" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Biblické filmy" dataDxfId="12"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0100-000016000000}" name="Pro děti" dataDxfId="11"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Životopisné filmy" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Rodinné filmy" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="České a slovenské filmy" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{9FCF2ECA-C3A0-43A8-A186-FD04B39FEE7B}" name="Plná velikost 2" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Filmy s dabingem" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Dokumenty" dataDxfId="5"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Seriály" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="Krátké filmy" dataDxfId="3"/>
+    <tableColumn id="18" xr3:uid="{BCC4A0AC-A4A9-436F-978E-493A75355B9F}" name="Poutnické filmy" dataDxfId="2"/>
+    <tableColumn id="23" xr3:uid="{02EEE25E-FE38-4681-9DDC-8551467119E3}" name="Misijní filmy" dataDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{0DCBE57E-EFCC-47FB-ACE3-E37987A22685}" name="Plná velikost 3" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Carousely a rozřazení aktuálníc-style 2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1836,10 +1842,11 @@
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.140625" customWidth="1"/>
-    <col min="2" max="2" width="41.85546875" customWidth="1"/>
+    <col min="2" max="2" width="38.28515625" customWidth="1"/>
     <col min="3" max="3" width="9" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" customWidth="1"/>
     <col min="6" max="6" width="16.5703125" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
     <col min="8" max="8" width="19.28515625" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="21.28515625" customWidth="1"/>
@@ -12781,7 +12788,7 @@
         <v>102</v>
       </c>
       <c r="Q154" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="R154" s="8" t="s">
         <v>103</v>
@@ -12803,7 +12810,9 @@
       </c>
     </row>
     <row r="155" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="18"/>
+      <c r="A155" s="18">
+        <v>552</v>
+      </c>
       <c r="B155" t="s">
         <v>171</v>
       </c>
@@ -12850,7 +12859,7 @@
         <v>102</v>
       </c>
       <c r="Q155" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="R155" s="8" t="s">
         <v>103</v>
@@ -12872,8 +12881,15 @@
       </c>
     </row>
     <row r="156" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="18"/>
-      <c r="C156" s="8"/>
+      <c r="A156" s="18">
+        <v>553</v>
+      </c>
+      <c r="B156" t="s">
+        <v>179</v>
+      </c>
+      <c r="C156" s="8">
+        <v>2</v>
+      </c>
       <c r="D156" s="8" t="s">
         <v>102</v>
       </c>
@@ -12884,7 +12900,7 @@
         <v>102</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H156" s="8" t="s">
         <v>102</v>
@@ -12908,7 +12924,7 @@
         <v>102</v>
       </c>
       <c r="O156" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P156" s="17" t="s">
         <v>102</v>
@@ -12923,7 +12939,7 @@
         <v>102</v>
       </c>
       <c r="T156" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="U156" s="17" t="s">
         <v>102</v>
@@ -12937,7 +12953,12 @@
     </row>
     <row r="157" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="18"/>
-      <c r="C157" s="8"/>
+      <c r="B157" t="s">
+        <v>180</v>
+      </c>
+      <c r="C157" s="8">
+        <v>1</v>
+      </c>
       <c r="D157" s="8" t="s">
         <v>102</v>
       </c>
@@ -12948,7 +12969,7 @@
         <v>102</v>
       </c>
       <c r="G157" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H157" s="8" t="s">
         <v>102</v>
@@ -12957,7 +12978,7 @@
         <v>102</v>
       </c>
       <c r="J157" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K157" s="8" t="s">
         <v>102</v>

--- a/databaze_filmu.xlsx
+++ b/databaze_filmu.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c678b8341a1804/Dokumenty/film-layout-manager_v3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="987" documentId="13_ncr:1_{F0DD17AA-57C3-401E-A619-37D4E16B6A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB3EB910-57F0-4C6D-BE2F-CDDE2A71A3E9}"/>
+  <xr:revisionPtr revIDLastSave="1024" documentId="13_ncr:1_{F0DD17AA-57C3-401E-A619-37D4E16B6A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C77C89D-5A0E-47B5-AD3D-EA51A9FEAD04}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="databaze_filmu" sheetId="3" r:id="rId1"/>
@@ -1954,7 +1954,7 @@
         <v>34</v>
       </c>
       <c r="C2" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>102</v>
@@ -2170,7 +2170,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>102</v>
@@ -2312,7 +2312,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>102</v>
@@ -2383,7 +2383,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>102</v>
@@ -2667,7 +2667,7 @@
         <v>3</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>102</v>
@@ -3093,7 +3093,7 @@
         <v>3</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>102</v>
@@ -3164,7 +3164,7 @@
         <v>2</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>102</v>
@@ -3232,7 +3232,7 @@
         <v>5</v>
       </c>
       <c r="C20" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>102</v>
@@ -3803,7 +3803,7 @@
         <v>4</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>102</v>
@@ -3942,7 +3942,7 @@
         <v>26</v>
       </c>
       <c r="C30" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>102</v>
@@ -4087,7 +4087,7 @@
         <v>3</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>102</v>
@@ -4158,7 +4158,7 @@
         <v>3</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>102</v>
@@ -4723,7 +4723,7 @@
         <v>92</v>
       </c>
       <c r="C41" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>102</v>
@@ -4939,7 +4939,7 @@
         <v>3</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>102</v>
@@ -5081,7 +5081,7 @@
         <v>3</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>102</v>
@@ -5152,7 +5152,7 @@
         <v>3</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>102</v>
@@ -5220,10 +5220,10 @@
         <v>112</v>
       </c>
       <c r="C48" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>102</v>
@@ -5433,10 +5433,10 @@
         <v>109</v>
       </c>
       <c r="C51" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>102</v>
@@ -5646,7 +5646,7 @@
         <v>11</v>
       </c>
       <c r="C54" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>102</v>
@@ -5859,10 +5859,10 @@
         <v>90</v>
       </c>
       <c r="C57" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>102</v>
@@ -6001,7 +6001,7 @@
         <v>68</v>
       </c>
       <c r="C59" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>103</v>
@@ -6072,7 +6072,7 @@
         <v>83</v>
       </c>
       <c r="C60" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>102</v>
@@ -6430,7 +6430,7 @@
         <v>3</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>102</v>
@@ -6498,7 +6498,7 @@
         <v>6</v>
       </c>
       <c r="C66" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>102</v>
@@ -6572,7 +6572,7 @@
         <v>2</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>102</v>
@@ -6640,10 +6640,10 @@
         <v>54</v>
       </c>
       <c r="C68" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>102</v>
@@ -6711,10 +6711,10 @@
         <v>21</v>
       </c>
       <c r="C69" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>102</v>
@@ -6853,7 +6853,7 @@
         <v>79</v>
       </c>
       <c r="C71" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>102</v>
@@ -7208,7 +7208,7 @@
         <v>71</v>
       </c>
       <c r="C76" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>103</v>
@@ -7424,7 +7424,7 @@
         <v>2</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>102</v>
@@ -7492,7 +7492,7 @@
         <v>89</v>
       </c>
       <c r="C80" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>103</v>
@@ -8276,7 +8276,7 @@
         <v>4</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E91" s="6" t="s">
         <v>102</v>
@@ -9838,7 +9838,7 @@
         <v>3</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E113" s="6" t="s">
         <v>102</v>
@@ -9977,7 +9977,7 @@
         <v>130</v>
       </c>
       <c r="C115" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>102</v>
@@ -10832,7 +10832,7 @@
         <v>2</v>
       </c>
       <c r="D127" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E127" s="8" t="s">
         <v>102</v>
@@ -10903,7 +10903,7 @@
         <v>2</v>
       </c>
       <c r="D128" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E128" s="8" t="s">
         <v>102</v>
@@ -11471,7 +11471,7 @@
         <v>2</v>
       </c>
       <c r="D136" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E136" s="8" t="s">
         <v>102</v>
@@ -11752,7 +11752,7 @@
         <v>156</v>
       </c>
       <c r="C140" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D140" s="8" t="s">
         <v>103</v>
@@ -12036,7 +12036,7 @@
         <v>160</v>
       </c>
       <c r="C144" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D144" s="8" t="s">
         <v>102</v>
@@ -12749,7 +12749,7 @@
         <v>2</v>
       </c>
       <c r="D154" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E154" s="8" t="s">
         <v>102</v>
@@ -12820,7 +12820,7 @@
         <v>3</v>
       </c>
       <c r="D155" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E155" s="8" t="s">
         <v>102</v>
@@ -12891,7 +12891,7 @@
         <v>2</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E156" s="8" t="s">
         <v>102</v>
@@ -12952,7 +12952,9 @@
       </c>
     </row>
     <row r="157" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="18"/>
+      <c r="A157" s="18">
+        <v>556</v>
+      </c>
       <c r="B157" t="s">
         <v>180</v>
       </c>

--- a/databaze_filmu.xlsx
+++ b/databaze_filmu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c678b8341a1804/Dokumenty/film-layout-manager_v3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1024" documentId="13_ncr:1_{F0DD17AA-57C3-401E-A619-37D4E16B6A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C77C89D-5A0E-47B5-AD3D-EA51A9FEAD04}"/>
+  <xr:revisionPtr revIDLastSave="1057" documentId="13_ncr:1_{F0DD17AA-57C3-401E-A619-37D4E16B6A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79726411-933A-4E4F-B37D-DAB468B77C00}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4219" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4179" uniqueCount="181">
   <si>
     <t>Jen samé krásné věci</t>
   </si>
@@ -402,18 +402,12 @@
     <t>Carlo Acutis - Misionář 2.0</t>
   </si>
   <si>
-    <t>Skrytá požehnání</t>
-  </si>
-  <si>
     <t>Všechno nebo nic: S. Clare Crockett</t>
   </si>
   <si>
     <t>Nebe v podzemí</t>
   </si>
   <si>
-    <t>Milost pro Harlem</t>
-  </si>
-  <si>
     <t>Nový duch</t>
   </si>
   <si>
@@ -583,6 +577,12 @@
   </si>
   <si>
     <t>Babettina hostina</t>
+  </si>
+  <si>
+    <t>Příběh Vánoc</t>
+  </si>
+  <si>
+    <t>Příběh Velikonoc</t>
   </si>
 </sst>
 </file>
@@ -1606,8 +1606,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="VŠECHNY_FILMY" displayName="VŠECHNY_FILMY" ref="A1:W203">
-  <autoFilter ref="A1:W203" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="VŠECHNY_FILMY" displayName="VŠECHNY_FILMY" ref="A1:W201">
+  <autoFilter ref="A1:W201" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}"/>
   <tableColumns count="23">
     <tableColumn id="21" xr3:uid="{AFA04DCF-6DDB-4478-A6A0-E666816366F4}" name="ID" dataDxfId="21"/>
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Film" dataDxfId="20"/>
@@ -1838,7 +1838,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:W203"/>
+  <dimension ref="A1:W201"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.140625" customWidth="1"/>
@@ -1877,19 +1877,19 @@
   <sheetData>
     <row r="1" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>40</v>
@@ -1922,7 +1922,7 @@
         <v>45</v>
       </c>
       <c r="P1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="Q1" s="2" t="s">
         <v>46</v>
@@ -1937,13 +1937,13 @@
         <v>2</v>
       </c>
       <c r="U1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="V1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="W1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
@@ -2170,7 +2170,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>102</v>
@@ -2312,7 +2312,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>102</v>
@@ -2383,7 +2383,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>102</v>
@@ -2667,7 +2667,7 @@
         <v>3</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>102</v>
@@ -3093,7 +3093,7 @@
         <v>3</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>102</v>
@@ -3164,7 +3164,7 @@
         <v>2</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>102</v>
@@ -3803,7 +3803,7 @@
         <v>4</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>102</v>
@@ -4087,7 +4087,7 @@
         <v>3</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>102</v>
@@ -4158,7 +4158,7 @@
         <v>3</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>102</v>
@@ -4655,7 +4655,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>102</v>
@@ -4925,7 +4925,7 @@
         <v>102</v>
       </c>
       <c r="W43" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
@@ -4939,7 +4939,7 @@
         <v>3</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>102</v>
@@ -5046,7 +5046,7 @@
         <v>102</v>
       </c>
       <c r="P45" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q45" s="6" t="s">
         <v>102</v>
@@ -5081,7 +5081,7 @@
         <v>3</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>102</v>
@@ -5152,7 +5152,7 @@
         <v>3</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>102</v>
@@ -5223,7 +5223,7 @@
         <v>3</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>102</v>
@@ -5436,7 +5436,7 @@
         <v>3</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>102</v>
@@ -5862,7 +5862,7 @@
         <v>4</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>102</v>
@@ -6430,7 +6430,7 @@
         <v>3</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>102</v>
@@ -6572,7 +6572,7 @@
         <v>2</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>102</v>
@@ -6643,7 +6643,7 @@
         <v>4</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>102</v>
@@ -6714,7 +6714,7 @@
         <v>3</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>102</v>
@@ -6785,7 +6785,7 @@
         <v>1</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>102</v>
@@ -7211,7 +7211,7 @@
         <v>1</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>102</v>
@@ -7424,7 +7424,7 @@
         <v>2</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>102</v>
@@ -7495,7 +7495,7 @@
         <v>1</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>102</v>
@@ -7531,7 +7531,7 @@
         <v>103</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q80" s="6" t="s">
         <v>102</v>
@@ -7850,7 +7850,7 @@
         <v>2</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E85" s="6" t="s">
         <v>102</v>
@@ -8199,7 +8199,7 @@
         <v>311</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C90" s="6">
         <v>2</v>
@@ -8276,7 +8276,7 @@
         <v>4</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E91" s="6" t="s">
         <v>102</v>
@@ -8847,7 +8847,7 @@
         <v>102</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F99" s="6" t="s">
         <v>102</v>
@@ -9057,7 +9057,7 @@
         <v>2</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>102</v>
@@ -9131,7 +9131,7 @@
         <v>102</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F103" s="6" t="s">
         <v>102</v>
@@ -9332,16 +9332,16 @@
     </row>
     <row r="106" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="18">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>120</v>
       </c>
       <c r="C106" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>102</v>
@@ -9350,7 +9350,7 @@
         <v>102</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H106" s="6" t="s">
         <v>102</v>
@@ -9359,7 +9359,7 @@
         <v>102</v>
       </c>
       <c r="J106" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K106" s="6" t="s">
         <v>102</v>
@@ -9368,7 +9368,7 @@
         <v>102</v>
       </c>
       <c r="M106" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N106" s="6" t="s">
         <v>102</v>
@@ -9383,7 +9383,7 @@
         <v>102</v>
       </c>
       <c r="R106" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S106" s="6" t="s">
         <v>102</v>
@@ -9403,7 +9403,7 @@
     </row>
     <row r="107" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="18">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>121</v>
@@ -9412,7 +9412,7 @@
         <v>2</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E107" s="6" t="s">
         <v>102</v>
@@ -9439,13 +9439,13 @@
         <v>102</v>
       </c>
       <c r="M107" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N107" s="6" t="s">
         <v>102</v>
       </c>
       <c r="O107" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P107" s="6" t="s">
         <v>102</v>
@@ -9474,13 +9474,13 @@
     </row>
     <row r="108" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="18">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>122</v>
       </c>
       <c r="C108" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>102</v>
@@ -9492,16 +9492,16 @@
         <v>102</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I108" s="6" t="s">
         <v>102</v>
       </c>
       <c r="J108" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K108" s="6" t="s">
         <v>102</v>
@@ -9516,7 +9516,7 @@
         <v>102</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>102</v>
@@ -9525,7 +9525,7 @@
         <v>102</v>
       </c>
       <c r="R108" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S108" s="6" t="s">
         <v>102</v>
@@ -9545,13 +9545,13 @@
     </row>
     <row r="109" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="18">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>123</v>
       </c>
       <c r="C109" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>102</v>
@@ -9563,16 +9563,16 @@
         <v>102</v>
       </c>
       <c r="G109" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I109" s="6" t="s">
         <v>102</v>
       </c>
       <c r="J109" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K109" s="6" t="s">
         <v>102</v>
@@ -9587,7 +9587,7 @@
         <v>102</v>
       </c>
       <c r="O109" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P109" s="6" t="s">
         <v>102</v>
@@ -9596,7 +9596,7 @@
         <v>102</v>
       </c>
       <c r="R109" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S109" s="6" t="s">
         <v>102</v>
@@ -9616,7 +9616,7 @@
     </row>
     <row r="110" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="18">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>124</v>
@@ -9625,7 +9625,7 @@
         <v>1</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>102</v>
@@ -9637,13 +9637,13 @@
         <v>103</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I110" s="6" t="s">
         <v>102</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K110" s="6" t="s">
         <v>102</v>
@@ -9673,7 +9673,7 @@
         <v>102</v>
       </c>
       <c r="T110" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="U110" s="6" t="s">
         <v>102</v>
@@ -9687,13 +9687,13 @@
     </row>
     <row r="111" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="18">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C111" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>102</v>
@@ -9729,7 +9729,7 @@
         <v>102</v>
       </c>
       <c r="O111" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P111" s="6" t="s">
         <v>102</v>
@@ -9750,7 +9750,7 @@
         <v>102</v>
       </c>
       <c r="V111" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="W111" s="6" t="s">
         <v>102</v>
@@ -9758,16 +9758,16 @@
     </row>
     <row r="112" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="18">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C112" s="6">
         <v>1</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>102</v>
@@ -9794,7 +9794,7 @@
         <v>102</v>
       </c>
       <c r="M112" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N112" s="6" t="s">
         <v>102</v>
@@ -9815,7 +9815,7 @@
         <v>102</v>
       </c>
       <c r="T112" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U112" s="6" t="s">
         <v>102</v>
@@ -9829,7 +9829,7 @@
     </row>
     <row r="113" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="18">
-        <v>357</v>
+        <v>373</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>128</v>
@@ -9838,7 +9838,7 @@
         <v>3</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E113" s="6" t="s">
         <v>102</v>
@@ -9880,19 +9880,19 @@
         <v>102</v>
       </c>
       <c r="R113" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S113" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T113" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U113" s="6" t="s">
         <v>102</v>
       </c>
       <c r="V113" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="W113" s="6" t="s">
         <v>102</v>
@@ -9900,7 +9900,7 @@
     </row>
     <row r="114" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="18">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>129</v>
@@ -9911,52 +9911,52 @@
       <c r="D114" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E114" s="6" t="s">
+      <c r="E114" s="8" t="s">
         <v>102</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="G114" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="I114" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="J114" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K114" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="L114" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="M114" s="6" t="s">
-        <v>103</v>
+      <c r="G114" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="H114" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="I114" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="J114" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="K114" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="L114" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="M114" s="8" t="s">
+        <v>102</v>
       </c>
       <c r="N114" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="O114" s="6" t="s">
+      <c r="O114" s="8" t="s">
         <v>102</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="Q114" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="R114" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="S114" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="T114" s="6" t="s">
+      <c r="Q114" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="R114" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="S114" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="T114" s="8" t="s">
         <v>102</v>
       </c>
       <c r="U114" s="6" t="s">
@@ -9971,152 +9971,152 @@
     </row>
     <row r="115" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="18">
-        <v>373</v>
-      </c>
-      <c r="B115" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C115" s="6">
-        <v>3</v>
+        <v>397</v>
+      </c>
+      <c r="B115" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="C115" s="8">
+        <v>1</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E115" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="F115" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G115" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H115" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="I115" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="J115" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K115" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="L115" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="M115" s="6" t="s">
-        <v>102</v>
+      <c r="E115" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="F115" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G115" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="H115" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="I115" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="J115" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="K115" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="L115" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="M115" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="N115" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="O115" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="P115" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q115" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="R115" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="S115" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="T115" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="U115" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="V115" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="W115" s="6" t="s">
+      <c r="O115" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="P115" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q115" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="R115" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="S115" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="T115" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="U115" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="V115" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="W115" s="11" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="116" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="18">
-        <v>393</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C116" s="6">
+        <v>406</v>
+      </c>
+      <c r="B116" t="s">
+        <v>135</v>
+      </c>
+      <c r="C116" s="8">
         <v>1</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E116" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="F116" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G116" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="H116" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="I116" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="J116" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="K116" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="L116" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="M116" s="8" t="s">
-        <v>102</v>
+      <c r="E116" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="F116" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G116" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="H116" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="I116" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="J116" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="K116" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="L116" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="M116" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="N116" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="O116" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="P116" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q116" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="R116" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="S116" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="T116" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="U116" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="V116" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="W116" s="6" t="s">
+      <c r="O116" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="P116" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q116" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="R116" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="S116" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="T116" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="U116" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="V116" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="W116" s="11" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="117" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="18">
-        <v>397</v>
-      </c>
-      <c r="B117" s="15" t="s">
-        <v>133</v>
+        <v>401</v>
+      </c>
+      <c r="B117" t="s">
+        <v>134</v>
       </c>
       <c r="C117" s="8">
         <v>1</v>
@@ -10134,7 +10134,7 @@
         <v>103</v>
       </c>
       <c r="H117" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I117" s="12" t="s">
         <v>102</v>
@@ -10149,7 +10149,7 @@
         <v>102</v>
       </c>
       <c r="M117" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N117" s="6" t="s">
         <v>102</v>
@@ -10184,10 +10184,10 @@
     </row>
     <row r="118" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="18">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="B118" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C118" s="8">
         <v>1</v>
@@ -10202,7 +10202,7 @@
         <v>102</v>
       </c>
       <c r="G118" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H118" s="12" t="s">
         <v>103</v>
@@ -10211,7 +10211,7 @@
         <v>102</v>
       </c>
       <c r="J118" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K118" s="12" t="s">
         <v>102</v>
@@ -10220,7 +10220,7 @@
         <v>102</v>
       </c>
       <c r="M118" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N118" s="6" t="s">
         <v>102</v>
@@ -10255,10 +10255,10 @@
     </row>
     <row r="119" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="18">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B119" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C119" s="8">
         <v>1</v>
@@ -10276,13 +10276,13 @@
         <v>103</v>
       </c>
       <c r="H119" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I119" s="12" t="s">
         <v>102</v>
       </c>
       <c r="J119" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K119" s="12" t="s">
         <v>102</v>
@@ -10294,7 +10294,7 @@
         <v>102</v>
       </c>
       <c r="N119" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O119" s="12" t="s">
         <v>102</v>
@@ -10326,155 +10326,155 @@
     </row>
     <row r="120" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="18">
-        <v>400</v>
+        <v>436</v>
       </c>
       <c r="B120" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C120" s="8">
-        <v>1</v>
-      </c>
-      <c r="D120" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E120" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="F120" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="G120" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H120" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="I120" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="J120" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="K120" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="L120" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="M120" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="N120" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="O120" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="P120" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q120" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="R120" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="S120" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="T120" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="U120" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="V120" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="W120" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D120" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E120" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="F120" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="G120" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="H120" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="I120" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="J120" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="K120" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="L120" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="M120" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="N120" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="O120" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="P120" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q120" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="R120" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="S120" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="T120" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="U120" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="V120" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="W120" s="17" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="121" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="18">
-        <v>399</v>
+        <v>442</v>
       </c>
       <c r="B121" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C121" s="8">
         <v>1</v>
       </c>
-      <c r="D121" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E121" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="F121" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="G121" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H121" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="I121" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="J121" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="K121" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="L121" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="M121" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="N121" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="O121" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="P121" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q121" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="R121" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="S121" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="T121" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="U121" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="V121" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="W121" s="11" t="s">
+      <c r="D121" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E121" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="F121" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="G121" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="H121" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="I121" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="J121" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="K121" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="L121" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="M121" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="N121" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="O121" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="P121" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q121" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="R121" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="S121" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="T121" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="U121" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="V121" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="W121" s="17" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="122" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="18">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="B122" t="s">
         <v>138</v>
       </c>
       <c r="C122" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D122" s="8" t="s">
         <v>102</v>
@@ -10486,7 +10486,7 @@
         <v>102</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H122" s="8" t="s">
         <v>102</v>
@@ -10504,13 +10504,13 @@
         <v>102</v>
       </c>
       <c r="M122" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N122" s="8" t="s">
         <v>102</v>
       </c>
       <c r="O122" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P122" s="17" t="s">
         <v>102</v>
@@ -10519,7 +10519,7 @@
         <v>102</v>
       </c>
       <c r="R122" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S122" s="8" t="s">
         <v>102</v>
@@ -10539,7 +10539,7 @@
     </row>
     <row r="123" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="18">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B123" t="s">
         <v>139</v>
@@ -10566,10 +10566,10 @@
         <v>102</v>
       </c>
       <c r="J123" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K123" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L123" s="10" t="s">
         <v>102</v>
@@ -10581,7 +10581,7 @@
         <v>102</v>
       </c>
       <c r="O123" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P123" s="17" t="s">
         <v>102</v>
@@ -10596,7 +10596,7 @@
         <v>102</v>
       </c>
       <c r="T123" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="U123" s="17" t="s">
         <v>102</v>
@@ -10610,7 +10610,7 @@
     </row>
     <row r="124" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="18">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B124" t="s">
         <v>140</v>
@@ -10646,7 +10646,7 @@
         <v>102</v>
       </c>
       <c r="M124" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N124" s="8" t="s">
         <v>102</v>
@@ -10658,7 +10658,7 @@
         <v>102</v>
       </c>
       <c r="Q124" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="R124" s="8" t="s">
         <v>102</v>
@@ -10667,7 +10667,7 @@
         <v>102</v>
       </c>
       <c r="T124" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U124" s="17" t="s">
         <v>102</v>
@@ -10681,13 +10681,13 @@
     </row>
     <row r="125" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="18">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B125" t="s">
         <v>141</v>
       </c>
       <c r="C125" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D125" s="8" t="s">
         <v>102</v>
@@ -10711,7 +10711,7 @@
         <v>102</v>
       </c>
       <c r="K125" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L125" s="10" t="s">
         <v>102</v>
@@ -10735,10 +10735,10 @@
         <v>102</v>
       </c>
       <c r="S125" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T125" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U125" s="17" t="s">
         <v>102</v>
@@ -10752,16 +10752,16 @@
     </row>
     <row r="126" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="18">
-        <v>445</v>
+        <v>471</v>
       </c>
       <c r="B126" t="s">
         <v>142</v>
       </c>
       <c r="C126" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D126" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E126" s="8" t="s">
         <v>102</v>
@@ -10770,7 +10770,7 @@
         <v>102</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H126" s="8" t="s">
         <v>102</v>
@@ -10788,7 +10788,7 @@
         <v>102</v>
       </c>
       <c r="M126" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N126" s="8" t="s">
         <v>102</v>
@@ -10800,10 +10800,10 @@
         <v>102</v>
       </c>
       <c r="Q126" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R126" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S126" s="8" t="s">
         <v>102</v>
@@ -10823,16 +10823,16 @@
     </row>
     <row r="127" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="18">
-        <v>446</v>
+        <v>475</v>
       </c>
       <c r="B127" t="s">
         <v>143</v>
       </c>
       <c r="C127" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D127" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E127" s="8" t="s">
         <v>102</v>
@@ -10874,10 +10874,10 @@
         <v>102</v>
       </c>
       <c r="R127" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S127" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T127" s="8" t="s">
         <v>102</v>
@@ -10894,13 +10894,13 @@
     </row>
     <row r="128" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="18">
-        <v>471</v>
+        <v>440</v>
       </c>
       <c r="B128" t="s">
         <v>144</v>
       </c>
       <c r="C128" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D128" s="8" t="s">
         <v>103</v>
@@ -10912,7 +10912,7 @@
         <v>102</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H128" s="8" t="s">
         <v>102</v>
@@ -10921,7 +10921,7 @@
         <v>102</v>
       </c>
       <c r="J128" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K128" s="8" t="s">
         <v>102</v>
@@ -10930,7 +10930,7 @@
         <v>102</v>
       </c>
       <c r="M128" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N128" s="8" t="s">
         <v>102</v>
@@ -10945,7 +10945,7 @@
         <v>102</v>
       </c>
       <c r="R128" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S128" s="8" t="s">
         <v>102</v>
@@ -10965,13 +10965,13 @@
     </row>
     <row r="129" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="18">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="B129" t="s">
         <v>145</v>
       </c>
       <c r="C129" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D129" s="8" t="s">
         <v>102</v>
@@ -10992,7 +10992,7 @@
         <v>102</v>
       </c>
       <c r="J129" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K129" s="8" t="s">
         <v>102</v>
@@ -11007,7 +11007,7 @@
         <v>102</v>
       </c>
       <c r="O129" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P129" s="17" t="s">
         <v>102</v>
@@ -11016,7 +11016,7 @@
         <v>102</v>
       </c>
       <c r="R129" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S129" s="8" t="s">
         <v>102</v>
@@ -11036,10 +11036,10 @@
     </row>
     <row r="130" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="18">
-        <v>440</v>
+        <v>481</v>
       </c>
       <c r="B130" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C130" s="8">
         <v>1</v>
@@ -11054,7 +11054,7 @@
         <v>102</v>
       </c>
       <c r="G130" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H130" s="8" t="s">
         <v>102</v>
@@ -11063,7 +11063,7 @@
         <v>102</v>
       </c>
       <c r="J130" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K130" s="8" t="s">
         <v>102</v>
@@ -11084,7 +11084,7 @@
         <v>102</v>
       </c>
       <c r="Q130" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="R130" s="8" t="s">
         <v>102</v>
@@ -11107,10 +11107,10 @@
     </row>
     <row r="131" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="18">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B131" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C131" s="8">
         <v>1</v>
@@ -11128,7 +11128,7 @@
         <v>102</v>
       </c>
       <c r="H131" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I131" s="8" t="s">
         <v>102</v>
@@ -11149,13 +11149,13 @@
         <v>102</v>
       </c>
       <c r="O131" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P131" s="17" t="s">
         <v>102</v>
       </c>
       <c r="Q131" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="R131" s="8" t="s">
         <v>102</v>
@@ -11178,7 +11178,7 @@
     </row>
     <row r="132" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="18">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="B132" t="s">
         <v>149</v>
@@ -11205,7 +11205,7 @@
         <v>102</v>
       </c>
       <c r="J132" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K132" s="8" t="s">
         <v>102</v>
@@ -11214,7 +11214,7 @@
         <v>102</v>
       </c>
       <c r="M132" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N132" s="8" t="s">
         <v>102</v>
@@ -11244,15 +11244,15 @@
         <v>102</v>
       </c>
       <c r="W132" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="133" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="18">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B133" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C133" s="8">
         <v>1</v>
@@ -11270,7 +11270,7 @@
         <v>102</v>
       </c>
       <c r="H133" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I133" s="8" t="s">
         <v>102</v>
@@ -11297,7 +11297,7 @@
         <v>102</v>
       </c>
       <c r="Q133" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R133" s="8" t="s">
         <v>102</v>
@@ -11320,13 +11320,13 @@
     </row>
     <row r="134" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="18">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B134" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C134" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D134" s="8" t="s">
         <v>102</v>
@@ -11347,7 +11347,7 @@
         <v>102</v>
       </c>
       <c r="J134" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K134" s="8" t="s">
         <v>102</v>
@@ -11368,10 +11368,10 @@
         <v>102</v>
       </c>
       <c r="Q134" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R134" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S134" s="8" t="s">
         <v>102</v>
@@ -11391,10 +11391,10 @@
     </row>
     <row r="135" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="18">
-        <v>491</v>
+        <v>507</v>
       </c>
       <c r="B135" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C135" s="8">
         <v>1</v>
@@ -11409,7 +11409,7 @@
         <v>102</v>
       </c>
       <c r="G135" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H135" s="8" t="s">
         <v>102</v>
@@ -11418,10 +11418,10 @@
         <v>102</v>
       </c>
       <c r="J135" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K135" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L135" s="10" t="s">
         <v>102</v>
@@ -11430,7 +11430,7 @@
         <v>102</v>
       </c>
       <c r="N135" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O135" s="8" t="s">
         <v>102</v>
@@ -11462,16 +11462,16 @@
     </row>
     <row r="136" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="18">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="B136" t="s">
         <v>152</v>
       </c>
       <c r="C136" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D136" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E136" s="8" t="s">
         <v>102</v>
@@ -11480,7 +11480,7 @@
         <v>102</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H136" s="8" t="s">
         <v>102</v>
@@ -11492,7 +11492,7 @@
         <v>102</v>
       </c>
       <c r="K136" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L136" s="10" t="s">
         <v>102</v>
@@ -11513,7 +11513,7 @@
         <v>102</v>
       </c>
       <c r="R136" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S136" s="8" t="s">
         <v>102</v>
@@ -11533,7 +11533,7 @@
     </row>
     <row r="137" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="18">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B137" t="s">
         <v>153</v>
@@ -11560,10 +11560,10 @@
         <v>102</v>
       </c>
       <c r="J137" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K137" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L137" s="10" t="s">
         <v>102</v>
@@ -11572,7 +11572,7 @@
         <v>102</v>
       </c>
       <c r="N137" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O137" s="8" t="s">
         <v>102</v>
@@ -11604,16 +11604,16 @@
     </row>
     <row r="138" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="18">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="B138" t="s">
         <v>154</v>
       </c>
       <c r="C138" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D138" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E138" s="8" t="s">
         <v>102</v>
@@ -11622,7 +11622,7 @@
         <v>102</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H138" s="8" t="s">
         <v>102</v>
@@ -11634,7 +11634,7 @@
         <v>102</v>
       </c>
       <c r="K138" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L138" s="10" t="s">
         <v>102</v>
@@ -11655,7 +11655,7 @@
         <v>102</v>
       </c>
       <c r="R138" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S138" s="8" t="s">
         <v>102</v>
@@ -11673,9 +11673,9 @@
         <v>102</v>
       </c>
     </row>
-    <row r="139" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="18">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B139" t="s">
         <v>155</v>
@@ -11684,7 +11684,7 @@
         <v>1</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E139" s="8" t="s">
         <v>102</v>
@@ -11693,10 +11693,10 @@
         <v>102</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H139" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I139" s="8" t="s">
         <v>102</v>
@@ -11744,18 +11744,18 @@
         <v>102</v>
       </c>
     </row>
-    <row r="140" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="18">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="B140" t="s">
         <v>156</v>
       </c>
       <c r="C140" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D140" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E140" s="8" t="s">
         <v>102</v>
@@ -11764,7 +11764,7 @@
         <v>102</v>
       </c>
       <c r="G140" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H140" s="8" t="s">
         <v>102</v>
@@ -11776,7 +11776,7 @@
         <v>102</v>
       </c>
       <c r="K140" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L140" s="10" t="s">
         <v>102</v>
@@ -11785,7 +11785,7 @@
         <v>102</v>
       </c>
       <c r="N140" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O140" s="8" t="s">
         <v>102</v>
@@ -11797,7 +11797,7 @@
         <v>102</v>
       </c>
       <c r="R140" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S140" s="8" t="s">
         <v>102</v>
@@ -11817,7 +11817,7 @@
     </row>
     <row r="141" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="18">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B141" t="s">
         <v>157</v>
@@ -11826,7 +11826,7 @@
         <v>1</v>
       </c>
       <c r="D141" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E141" s="8" t="s">
         <v>102</v>
@@ -11838,28 +11838,28 @@
         <v>102</v>
       </c>
       <c r="H141" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I141" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J141" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K141" s="8" t="s">
         <v>102</v>
       </c>
       <c r="L141" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M141" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N141" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O141" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P141" s="17" t="s">
         <v>102</v>
@@ -11874,7 +11874,7 @@
         <v>102</v>
       </c>
       <c r="T141" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="U141" s="17" t="s">
         <v>102</v>
@@ -11888,13 +11888,13 @@
     </row>
     <row r="142" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="18">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="B142" t="s">
         <v>158</v>
       </c>
       <c r="C142" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D142" s="8" t="s">
         <v>102</v>
@@ -11906,7 +11906,7 @@
         <v>102</v>
       </c>
       <c r="G142" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H142" s="8" t="s">
         <v>102</v>
@@ -11915,10 +11915,10 @@
         <v>102</v>
       </c>
       <c r="J142" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K142" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L142" s="10" t="s">
         <v>102</v>
@@ -11927,10 +11927,10 @@
         <v>102</v>
       </c>
       <c r="N142" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O142" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P142" s="17" t="s">
         <v>102</v>
@@ -11959,7 +11959,7 @@
     </row>
     <row r="143" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="18">
-        <v>516</v>
+        <v>500</v>
       </c>
       <c r="B143" t="s">
         <v>159</v>
@@ -11968,7 +11968,7 @@
         <v>1</v>
       </c>
       <c r="D143" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E143" s="8" t="s">
         <v>102</v>
@@ -11983,7 +11983,7 @@
         <v>102</v>
       </c>
       <c r="I143" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J143" s="8" t="s">
         <v>102</v>
@@ -11992,22 +11992,22 @@
         <v>102</v>
       </c>
       <c r="L143" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M143" s="8" t="s">
         <v>103</v>
       </c>
       <c r="N143" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O143" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P143" s="17" t="s">
         <v>102</v>
       </c>
       <c r="Q143" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="R143" s="8" t="s">
         <v>102</v>
@@ -12016,7 +12016,7 @@
         <v>102</v>
       </c>
       <c r="T143" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U143" s="17" t="s">
         <v>102</v>
@@ -12030,13 +12030,13 @@
     </row>
     <row r="144" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="18">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="B144" t="s">
         <v>160</v>
       </c>
       <c r="C144" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D144" s="8" t="s">
         <v>102</v>
@@ -12072,7 +12072,7 @@
         <v>102</v>
       </c>
       <c r="O144" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P144" s="17" t="s">
         <v>102</v>
@@ -12087,7 +12087,7 @@
         <v>102</v>
       </c>
       <c r="T144" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="U144" s="17" t="s">
         <v>102</v>
@@ -12101,7 +12101,7 @@
     </row>
     <row r="145" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="18">
-        <v>500</v>
+        <v>524</v>
       </c>
       <c r="B145" t="s">
         <v>161</v>
@@ -12119,7 +12119,7 @@
         <v>102</v>
       </c>
       <c r="G145" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H145" s="8" t="s">
         <v>102</v>
@@ -12128,7 +12128,7 @@
         <v>102</v>
       </c>
       <c r="J145" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K145" s="8" t="s">
         <v>102</v>
@@ -12137,10 +12137,10 @@
         <v>102</v>
       </c>
       <c r="M145" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N145" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O145" s="8" t="s">
         <v>102</v>
@@ -12149,7 +12149,7 @@
         <v>102</v>
       </c>
       <c r="Q145" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R145" s="8" t="s">
         <v>102</v>
@@ -12172,7 +12172,7 @@
     </row>
     <row r="146" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="18">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="B146" t="s">
         <v>162</v>
@@ -12190,7 +12190,7 @@
         <v>102</v>
       </c>
       <c r="G146" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H146" s="8" t="s">
         <v>102</v>
@@ -12211,7 +12211,7 @@
         <v>102</v>
       </c>
       <c r="N146" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O146" s="8" t="s">
         <v>102</v>
@@ -12229,7 +12229,7 @@
         <v>102</v>
       </c>
       <c r="T146" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U146" s="17" t="s">
         <v>102</v>
@@ -12243,7 +12243,7 @@
     </row>
     <row r="147" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="18">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B147" t="s">
         <v>163</v>
@@ -12282,7 +12282,7 @@
         <v>102</v>
       </c>
       <c r="N147" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O147" s="8" t="s">
         <v>102</v>
@@ -12314,7 +12314,7 @@
     </row>
     <row r="148" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="18">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B148" t="s">
         <v>164</v>
@@ -12332,7 +12332,7 @@
         <v>102</v>
       </c>
       <c r="G148" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H148" s="8" t="s">
         <v>102</v>
@@ -12353,7 +12353,7 @@
         <v>102</v>
       </c>
       <c r="N148" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O148" s="8" t="s">
         <v>102</v>
@@ -12385,7 +12385,7 @@
     </row>
     <row r="149" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="18">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="B149" t="s">
         <v>165</v>
@@ -12403,7 +12403,7 @@
         <v>102</v>
       </c>
       <c r="G149" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H149" s="8" t="s">
         <v>102</v>
@@ -12456,7 +12456,7 @@
     </row>
     <row r="150" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="18">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="B150" t="s">
         <v>166</v>
@@ -12483,7 +12483,7 @@
         <v>102</v>
       </c>
       <c r="J150" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K150" s="8" t="s">
         <v>102</v>
@@ -12495,7 +12495,7 @@
         <v>102</v>
       </c>
       <c r="N150" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O150" s="8" t="s">
         <v>102</v>
@@ -12527,7 +12527,7 @@
     </row>
     <row r="151" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="18">
-        <v>535</v>
+        <v>545</v>
       </c>
       <c r="B151" t="s">
         <v>167</v>
@@ -12548,7 +12548,7 @@
         <v>102</v>
       </c>
       <c r="H151" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I151" s="8" t="s">
         <v>102</v>
@@ -12598,13 +12598,13 @@
     </row>
     <row r="152" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="18">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="B152" t="s">
         <v>168</v>
       </c>
       <c r="C152" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D152" s="8" t="s">
         <v>102</v>
@@ -12637,7 +12637,7 @@
         <v>102</v>
       </c>
       <c r="N152" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O152" s="8" t="s">
         <v>102</v>
@@ -12646,10 +12646,10 @@
         <v>102</v>
       </c>
       <c r="Q152" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="R152" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S152" s="8" t="s">
         <v>102</v>
@@ -12661,7 +12661,7 @@
         <v>102</v>
       </c>
       <c r="V152" s="17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="W152" s="17" t="s">
         <v>102</v>
@@ -12669,13 +12669,13 @@
     </row>
     <row r="153" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="18">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="B153" t="s">
         <v>169</v>
       </c>
       <c r="C153" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D153" s="8" t="s">
         <v>102</v>
@@ -12690,13 +12690,13 @@
         <v>102</v>
       </c>
       <c r="H153" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I153" s="8" t="s">
         <v>102</v>
       </c>
       <c r="J153" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K153" s="8" t="s">
         <v>102</v>
@@ -12717,22 +12717,22 @@
         <v>102</v>
       </c>
       <c r="Q153" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="R153" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S153" s="8" t="s">
         <v>102</v>
       </c>
       <c r="T153" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="U153" s="17" t="s">
         <v>102</v>
       </c>
       <c r="V153" s="17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="W153" s="17" t="s">
         <v>102</v>
@@ -12740,16 +12740,16 @@
     </row>
     <row r="154" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="18">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B154" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C154" s="8">
         <v>2</v>
       </c>
       <c r="D154" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E154" s="8" t="s">
         <v>102</v>
@@ -12758,7 +12758,7 @@
         <v>102</v>
       </c>
       <c r="G154" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H154" s="8" t="s">
         <v>102</v>
@@ -12782,28 +12782,28 @@
         <v>102</v>
       </c>
       <c r="O154" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P154" s="17" t="s">
         <v>102</v>
       </c>
       <c r="Q154" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R154" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S154" s="8" t="s">
         <v>102</v>
       </c>
       <c r="T154" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="U154" s="17" t="s">
         <v>102</v>
       </c>
       <c r="V154" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="W154" s="17" t="s">
         <v>102</v>
@@ -12811,16 +12811,16 @@
     </row>
     <row r="155" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="18">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B155" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C155" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D155" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E155" s="8" t="s">
         <v>102</v>
@@ -12829,7 +12829,7 @@
         <v>102</v>
       </c>
       <c r="G155" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H155" s="8" t="s">
         <v>102</v>
@@ -12838,7 +12838,7 @@
         <v>102</v>
       </c>
       <c r="J155" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K155" s="8" t="s">
         <v>102</v>
@@ -12859,22 +12859,22 @@
         <v>102</v>
       </c>
       <c r="Q155" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R155" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S155" s="8" t="s">
         <v>102</v>
       </c>
       <c r="T155" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U155" s="17" t="s">
         <v>102</v>
       </c>
       <c r="V155" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="W155" s="17" t="s">
         <v>102</v>
@@ -12882,16 +12882,16 @@
     </row>
     <row r="156" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="18">
-        <v>553</v>
+        <v>202</v>
       </c>
       <c r="B156" t="s">
         <v>179</v>
       </c>
       <c r="C156" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E156" s="8" t="s">
         <v>102</v>
@@ -12900,7 +12900,7 @@
         <v>102</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H156" s="8" t="s">
         <v>102</v>
@@ -12915,16 +12915,16 @@
         <v>102</v>
       </c>
       <c r="L156" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M156" s="8" t="s">
         <v>102</v>
       </c>
       <c r="N156" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O156" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P156" s="17" t="s">
         <v>102</v>
@@ -12939,7 +12939,7 @@
         <v>102</v>
       </c>
       <c r="T156" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U156" s="17" t="s">
         <v>102</v>
@@ -12953,7 +12953,7 @@
     </row>
     <row r="157" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="18">
-        <v>556</v>
+        <v>281</v>
       </c>
       <c r="B157" t="s">
         <v>180</v>
@@ -12971,7 +12971,7 @@
         <v>102</v>
       </c>
       <c r="G157" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H157" s="8" t="s">
         <v>102</v>
@@ -12980,19 +12980,19 @@
         <v>102</v>
       </c>
       <c r="J157" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K157" s="8" t="s">
         <v>102</v>
       </c>
       <c r="L157" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M157" s="8" t="s">
         <v>102</v>
       </c>
       <c r="N157" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O157" s="8" t="s">
         <v>102</v>
@@ -13482,7 +13482,7 @@
       <c r="F165" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="G165" s="8" t="s">
+      <c r="G165" s="6" t="s">
         <v>102</v>
       </c>
       <c r="H165" s="8" t="s">
@@ -13503,7 +13503,7 @@
       <c r="M165" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="N165" s="8" t="s">
+      <c r="N165" s="6" t="s">
         <v>102</v>
       </c>
       <c r="O165" s="8" t="s">
@@ -13610,7 +13610,7 @@
       <c r="F167" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="G167" s="6" t="s">
+      <c r="G167" s="8" t="s">
         <v>102</v>
       </c>
       <c r="H167" s="8" t="s">
@@ -13631,7 +13631,7 @@
       <c r="M167" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="N167" s="6" t="s">
+      <c r="N167" s="8" t="s">
         <v>102</v>
       </c>
       <c r="O167" s="8" t="s">
@@ -13674,7 +13674,7 @@
       <c r="F168" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="G168" s="8" t="s">
+      <c r="G168" s="6" t="s">
         <v>102</v>
       </c>
       <c r="H168" s="8" t="s">
@@ -13695,7 +13695,7 @@
       <c r="M168" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="N168" s="8" t="s">
+      <c r="N168" s="6" t="s">
         <v>102</v>
       </c>
       <c r="O168" s="8" t="s">
@@ -15835,134 +15835,6 @@
         <v>102</v>
       </c>
       <c r="W201" s="17" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="202" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A202" s="18"/>
-      <c r="C202" s="8"/>
-      <c r="D202" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="E202" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="F202" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="G202" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H202" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="I202" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="J202" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="K202" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="L202" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="M202" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="N202" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="O202" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="P202" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q202" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="R202" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="S202" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="T202" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="U202" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="V202" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="W202" s="17" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="203" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A203" s="18"/>
-      <c r="C203" s="8"/>
-      <c r="D203" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="E203" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="F203" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="G203" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="H203" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="I203" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="J203" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="K203" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="L203" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="M203" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="N203" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="O203" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="P203" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q203" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="R203" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="S203" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="T203" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="U203" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="V203" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="W203" s="17" t="s">
         <v>102</v>
       </c>
     </row>
